--- a/evaluation/results/Qualitative Evaluations - System 1, System 2 and System 3/LLMs4Subjects-Evaluation-Sheet-lit.xlsx
+++ b/evaluation/results/Qualitative Evaluations - System 1, System 2 and System 3/LLMs4Subjects-Evaluation-Sheet-lit.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SadruddinS\Data\GermEval25\Qualitative Evaluations\Evaluation with LA2I2F\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSouzaJ\Datasets\subject-indexing-dataset\evaluation\results\Qualitative Evaluations - System 1, System 2 and System 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BA7031-1F38-4AED-97EE-AEFBBBB407A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14100" tabRatio="500"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LLMs4Subjects Evaluation Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -1004,22 +1008,22 @@
     <t>Erlebnisbericht | gnd:4133254-4</t>
   </si>
   <si>
-    <t>LA2I2F - Team 1</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
-    <t>DNB-AI - Team 2</t>
-  </si>
-  <si>
-    <t>Annif - Team 3</t>
+    <t>System 1</t>
+  </si>
+  <si>
+    <t>System 2</t>
+  </si>
+  <si>
+    <t>System 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1272,7 +1276,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K201"/>
   <sheetFormatPr defaultColWidth="52.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1306,22 +1310,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>328</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>329</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
